--- a/Docs/武器动画描述.xlsx
+++ b/Docs/武器动画描述.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="89">
   <si>
     <t>资源文件名</t>
   </si>
@@ -37,24 +37,75 @@
     <t>功能描述</t>
   </si>
   <si>
+    <t>发力手</t>
+  </si>
+  <si>
+    <t>发力姿势-躯干</t>
+  </si>
+  <si>
+    <t>发力姿势-手部前后位置</t>
+  </si>
+  <si>
+    <t>发力姿势-手部高度</t>
+  </si>
+  <si>
+    <t>收力姿势</t>
+  </si>
+  <si>
+    <t>发力姿势-发力手高度</t>
+  </si>
+  <si>
     <t>TwinSword_Air_Attack_1</t>
   </si>
   <si>
     <t>空右下起双斜斩</t>
   </si>
   <si>
+    <t>右手</t>
+  </si>
+  <si>
+    <t>身体右转60度左右</t>
+  </si>
+  <si>
+    <t>左手身前,右手身后</t>
+  </si>
+  <si>
+    <t>左手肩高,右手腰高</t>
+  </si>
+  <si>
+    <t>身体左转90度左右</t>
+  </si>
+  <si>
+    <t>左手身后,右手身前</t>
+  </si>
+  <si>
+    <t>左手腰高,右手肩高</t>
+  </si>
+  <si>
     <t>TwinSword_Air_Attack_2</t>
   </si>
   <si>
     <t>空左下起双斜斩</t>
   </si>
   <si>
+    <t>左手</t>
+  </si>
+  <si>
+    <t>身体右转90度左右</t>
+  </si>
+  <si>
     <t>TwinSword_Air_Attack_3</t>
   </si>
   <si>
     <t>空左上起双斜斩</t>
   </si>
   <si>
+    <t>身体左转130度左右</t>
+  </si>
+  <si>
+    <t>身体右转130度左右</t>
+  </si>
+  <si>
     <t>TwinSword_Air_Attack_4</t>
   </si>
   <si>
@@ -67,18 +118,36 @@
     <t>空双竖劈</t>
   </si>
   <si>
+    <t>左手头高,右手头高</t>
+  </si>
+  <si>
+    <t>左手身前,右手身前</t>
+  </si>
+  <si>
+    <t>左手腰高,右手头高</t>
+  </si>
+  <si>
     <t>TwinSword_Air_Attack_6</t>
   </si>
   <si>
     <t>空翻滚连续竖劈接落地</t>
   </si>
   <si>
+    <t>身体左转60度左右</t>
+  </si>
+  <si>
+    <t>左手腰高,右手腰高</t>
+  </si>
+  <si>
     <t>TwinSword_Air_Attack_6_End</t>
   </si>
   <si>
     <t>空到落地</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>TwinSword_Air_Attack_6_Loop</t>
   </si>
   <si>
@@ -97,12 +166,21 @@
     <t>左上起双斜斩</t>
   </si>
   <si>
+    <t>左手头高,右手肩高</t>
+  </si>
+  <si>
+    <t>左手肩高,右手肩高</t>
+  </si>
+  <si>
     <t>TwinSword_Attack14</t>
   </si>
   <si>
     <t>右上起双斜斩</t>
   </si>
   <si>
+    <t>左手肩高,右手头高</t>
+  </si>
+  <si>
     <t>TwinSword_Attack15</t>
   </si>
   <si>
@@ -121,6 +199,12 @@
     <t>右上起双斜斩接转身横扫</t>
   </si>
   <si>
+    <t>身体正向前倾</t>
+  </si>
+  <si>
+    <t>左手身后,右手身后</t>
+  </si>
+  <si>
     <t>TwinSword_Attack18</t>
   </si>
   <si>
@@ -191,6 +275,9 @@
   </si>
   <si>
     <t>右手上挑进入腾空状态</t>
+  </si>
+  <si>
+    <t>身体正向腾空状态</t>
   </si>
   <si>
     <t>TwinSword_Attack30</t>
@@ -1139,251 +1226,720 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <dimension ref="A1:I30"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="31.5" customWidth="1"/>
-    <col min="2" max="2" width="8.875" customWidth="1"/>
+    <col min="2" max="2" width="31.625" customWidth="1"/>
+    <col min="3" max="3" width="7" customWidth="1"/>
+    <col min="4" max="4" width="18.375" customWidth="1"/>
+    <col min="5" max="5" width="22.375" customWidth="1"/>
+    <col min="6" max="6" width="20.25" customWidth="1"/>
+    <col min="7" max="7" width="18.375" customWidth="1"/>
+    <col min="8" max="8" width="22.375" customWidth="1"/>
+    <col min="9" max="9" width="20.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
         <v>10</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" t="s">
+        <v>56</v>
+      </c>
+      <c r="H16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" t="s">
+        <v>56</v>
+      </c>
+      <c r="H17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G18" t="s">
+        <v>56</v>
+      </c>
+      <c r="H18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
+      <c r="E19" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
+      <c r="G19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H20" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" t="s">
+        <v>30</v>
+      </c>
+      <c r="G21" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" t="s">
         <v>14</v>
       </c>
-      <c r="B8" t="s">
+      <c r="H23" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
+      <c r="D24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" t="s">
         <v>20</v>
       </c>
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="H24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" t="s">
+        <v>77</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
+      <c r="E26" t="s">
+        <v>15</v>
+      </c>
+      <c r="G26" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
+        <v>80</v>
+      </c>
+      <c r="B27" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" t="s">
         <v>24</v>
       </c>
-      <c r="B13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" t="s">
+        <v>83</v>
+      </c>
+      <c r="B28" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" t="s">
+        <v>85</v>
+      </c>
+      <c r="B29" t="s">
+        <v>86</v>
+      </c>
+      <c r="C29" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>57</v>
+      </c>
+      <c r="G29" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" t="s">
         <v>34</v>
       </c>
-      <c r="B18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" t="s">
-        <v>56</v>
-      </c>
-      <c r="B29" t="s">
+      <c r="E30" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" t="s">
-        <v>58</v>
-      </c>
-      <c r="B30" t="s">
-        <v>59</v>
+      <c r="G30" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
